--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487967_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487967_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0221</v>
+        <v>1.5149</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.192</v>
+        <v>0.3008</v>
       </c>
       <c r="F2" t="n">
         <v>1.2142</v>
@@ -610,10 +610,10 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9911</v>
+        <v>-0.4983</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2458</v>
+        <v>0.247</v>
       </c>
       <c r="U2" t="n">
         <v>-0.7453</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3997</v>
+        <v>0.6876</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.7718</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1683</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.8715000000000001</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8505</v>
+        <v>-0.5625</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5616</v>
+        <v>-0.3578</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2889</v>
+        <v>-0.2047</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2071</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0915</v>
+        <v>-0.0559</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1031</v>
+        <v>0.4668</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1946</v>
+        <v>-0.5226</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5956</v>
+        <v>1.6252</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.6535</v>
+        <v>1.8509</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0578</v>
+        <v>-0.2258</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.1065</v>
+        <v>1.9571</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1908</v>
+        <v>1.9169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0842</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4891</v>
+        <v>-0.3319</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4627</v>
+        <v>-0.066</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9736</v>
+        <v>-0.266</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1716</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1716</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8063</v>
+        <v>-0.4056</v>
       </c>
       <c r="T4" t="n">
-        <v>1.41</v>
+        <v>-0.4992</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6037</v>
+        <v>0.0936</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4737</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2734</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.112</v>
+        <v>-0.3902</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4668</v>
+        <v>-0.3359</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5788</v>
+        <v>-0.0543</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6252</v>
+        <v>-0.6536</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8509</v>
+        <v>-1.0113</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2258</v>
+        <v>0.3577</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9571</v>
+        <v>-0.3296</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9169</v>
+        <v>-0.4099</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0.0804</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3319</v>
+        <v>-0.3241</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.066</v>
+        <v>-0.6014</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.266</v>
+        <v>0.2774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4617</v>
+        <v>-0.5295</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>-0.0064</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0374</v>
+        <v>-0.5231</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.752</v>
+        <v>-1.1372</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6415</v>
+        <v>-0.8302</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1105</v>
+        <v>-0.3069</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6536</v>
+        <v>-2.5956</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0113</v>
+        <v>-3.6535</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3577</v>
+        <v>1.0578</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3296</v>
+        <v>-2.1065</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4099</v>
+        <v>-2.1908</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0804</v>
+        <v>0.0842</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3241</v>
+        <v>-0.4891</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6014</v>
+        <v>-1.4627</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2774</v>
+        <v>0.9736</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>3.1716</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>3.1716</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8913</v>
+        <v>-0.2394</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.312</v>
+        <v>0.4766</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5793</v>
+        <v>-0.716</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.2734</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7773</v>
+        <v>-1.6473</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.314</v>
+        <v>-0.2122</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4632</v>
+        <v>-1.4351</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4751</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4915</v>
+        <v>-0.3615</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.28</v>
+        <v>-1.8558</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0269</v>
+        <v>0.3949</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3069</v>
+        <v>-2.2507</v>
       </c>
       <c r="G8" t="n">
         <v>-0.805</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4838</v>
+        <v>-0.0596</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2496</v>
+        <v>0.1184</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7169</v>
+        <v>-3.9321</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5183</v>
+        <v>-2.7615</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1987</v>
+        <v>-1.1706</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0939</v>
@@ -1156,13 +1156,13 @@
         <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.407</v>
+        <v>-0.6222</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1176</v>
+        <v>-0.1257</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5246</v>
+        <v>-0.4965</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6491</v>
+        <v>-4.2053</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5152</v>
+        <v>-3.8187</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1339</v>
+        <v>-0.3866</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9849</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.587</v>
+        <v>-0.1432</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3706</v>
+        <v>0.3259</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2164</v>
+        <v>-0.4691</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4737</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4242</v>
+        <v>-4.6382</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5103</v>
+        <v>-4.8367</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0861</v>
+        <v>0.1984</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3687</v>
@@ -1312,13 +1312,13 @@
         <v>2.3787</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1239</v>
+        <v>-1.3379</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4865</v>
+        <v>-0.8129</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6373</v>
+        <v>-0.525</v>
       </c>
       <c r="V11" t="n">
         <v>-0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2213</v>
+        <v>-7.9396</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8832</v>
+        <v>-4.5734</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3381</v>
+        <v>-3.3662</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4434</v>
@@ -1390,13 +1390,13 @@
         <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1209</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9804</v>
+        <v>0.2903</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8595</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2953</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.405799999999999</v>
+        <v>-8.4733</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4982</v>
+        <v>-6.5377</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9076</v>
+        <v>-1.9356</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0687</v>
@@ -1468,13 +1468,13 @@
         <v>2.9733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8702</v>
+        <v>-0.9378</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3889</v>
+        <v>-0.4283</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4814</v>
+        <v>-0.5094</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4846</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-33.0083</v>
+        <v>-32.0724</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.9079</v>
+        <v>-21.972</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.1003</v>
+        <v>-10.1001</v>
       </c>
       <c r="G14" t="n">
         <v>-14.5825</v>
@@ -1519,10 +1519,10 @@
         <v>-3.3672</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.459800000000001</v>
+        <v>-8.4598</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8754000000000005</v>
+        <v>-0.8753999999999996</v>
       </c>
       <c r="L14" t="n">
         <v>-7.584399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>18.8312</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.230799999999999</v>
+        <v>-6.2948</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9806</v>
+        <v>-1.0446</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.250299999999999</v>
+        <v>-5.2502</v>
       </c>
       <c r="V14" t="n">
         <v>-15.1593</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.7768</v>
+        <v>8.995799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1032</v>
+        <v>5.1863</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6736</v>
+        <v>3.8095</v>
       </c>
       <c r="G15" t="n">
         <v>4.18</v>
@@ -1624,13 +1624,13 @@
         <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1915</v>
+        <v>1.4105</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2173</v>
+        <v>1.3005</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0259</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
         <v>2.4142</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7092</v>
+        <v>7.7476</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8213</v>
+        <v>3.559</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8878</v>
+        <v>4.1886</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6185</v>
+        <v>1.6663</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9375</v>
+        <v>2.2057</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6808999999999999</v>
+        <v>-0.5394</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5493</v>
+        <v>0.0246</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1079</v>
+        <v>2.0581</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5586</v>
+        <v>-2.0335</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0692</v>
+        <v>1.6417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1704</v>
+        <v>0.1476</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2395</v>
+        <v>1.4941</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0.881</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7806</v>
+        <v>0.8536</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5004999999999999</v>
+        <v>0.0274</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4142</v>
+        <v>2.8216</v>
       </c>
       <c r="W16" t="n">
         <v>2.6808</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2666</v>
+        <v>0.1408</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.9444</v>
+        <v>7.5074</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9478</v>
+        <v>5.0064</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9966</v>
+        <v>2.501</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6663</v>
+        <v>3.6185</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2057</v>
+        <v>2.9375</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5394</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0246</v>
+        <v>2.5493</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0581</v>
+        <v>3.1079</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0335</v>
+        <v>-0.5586</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6417</v>
+        <v>1.0692</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1476</v>
+        <v>-0.1704</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4941</v>
+        <v>1.2395</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3787</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07779999999999999</v>
+        <v>1.0782</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2423</v>
+        <v>0.9656</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1646</v>
+        <v>0.1126</v>
       </c>
       <c r="V17" t="n">
-        <v>2.8216</v>
+        <v>2.4142</v>
       </c>
       <c r="W17" t="n">
         <v>2.6808</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1408</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.5068</v>
+        <v>4.3641</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1125</v>
+        <v>1.8901</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3943</v>
+        <v>2.474</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0424</v>
@@ -1858,13 +1858,13 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2054</v>
+        <v>1.0626</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3973</v>
+        <v>1.1749</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1919</v>
+        <v>-0.1122</v>
       </c>
       <c r="V18" t="n">
         <v>2.9474</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7402</v>
+        <v>3.3255</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1306</v>
+        <v>-0.4175</v>
       </c>
       <c r="F19" t="n">
-        <v>4.8707</v>
+        <v>3.743</v>
       </c>
       <c r="G19" t="n">
         <v>0.5883</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8149</v>
+        <v>1.4002</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8112</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>2.626</v>
+        <v>1.4983</v>
       </c>
       <c r="V19" t="n">
         <v>0.9405</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4799</v>
+        <v>3.3219</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8619</v>
+        <v>0.76</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6181</v>
+        <v>2.5619</v>
       </c>
       <c r="G20" t="n">
         <v>2.5138</v>
@@ -2014,13 +2014,13 @@
         <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8472</v>
+        <v>0.6891</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8591</v>
+        <v>0.7572</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0119</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.674</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3027</v>
+        <v>0.5484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3027</v>
+        <v>-0.9061</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.4545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3027</v>
+        <v>-0.3702</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3027</v>
+        <v>0.0871</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.4572</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3027</v>
+        <v>-1.0087</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3027</v>
+        <v>0.2692</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.2779</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.6385</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1822</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.8207</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.2972</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.1312</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.4284</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2117</v>
+        <v>0.3027</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2018</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3702</v>
+        <v>0.3027</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0871</v>
+        <v>0.3027</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4572</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0087</v>
+        <v>0.3027</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2692</v>
+        <v>0.3027</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2779</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6385</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1822</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8207</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2611</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4368</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1757</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2339</v>
+        <v>0.026</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4284</v>
+        <v>-2.2247</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1945</v>
+        <v>2.2507</v>
       </c>
       <c r="G24" t="n">
         <v>3.672</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3163</v>
+        <v>0.5762</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6283</v>
+        <v>0.6845</v>
       </c>
       <c r="V24" t="n">
         <v>0.337</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1329</v>
+        <v>-0.5113</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4044</v>
+        <v>-0.895</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2714</v>
+        <v>0.3838</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3377</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5198</v>
+        <v>0.1019</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1872</v>
+        <v>0.3222</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3326</v>
+        <v>-0.2203</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2666</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0273</v>
+        <v>-1.4056</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5653</v>
+        <v>-2.056</v>
       </c>
       <c r="F26" t="n">
-        <v>0.538</v>
+        <v>0.6503</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7324000000000001</v>
@@ -2482,13 +2482,13 @@
         <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5198</v>
+        <v>0.1019</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1872</v>
+        <v>0.3222</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3326</v>
+        <v>-0.2203</v>
       </c>
       <c r="V26" t="n">
         <v>1.2071</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.5584</v>
+        <v>-2.0458</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8193</v>
+        <v>-1.6155</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7391</v>
+        <v>-0.4302</v>
       </c>
       <c r="G27" t="n">
         <v>-0.987</v>
@@ -2560,13 +2560,13 @@
         <v>0.3964</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2016</v>
+        <v>0.311</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1104</v>
+        <v>0.4193</v>
       </c>
       <c r="V27" t="n">
         <v>1.2071</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>33.00830000000001</v>
+        <v>33.6874</v>
       </c>
       <c r="E28" t="n">
         <v>10.1004</v>
       </c>
       <c r="F28" t="n">
-        <v>22.9077</v>
+        <v>23.5871</v>
       </c>
       <c r="G28" t="n">
         <v>14.5826</v>
@@ -2611,19 +2611,19 @@
         <v>3.3672</v>
       </c>
       <c r="J28" t="n">
-        <v>6.1227</v>
+        <v>6.122699999999998</v>
       </c>
       <c r="K28" t="n">
         <v>10.3401</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.217300000000001</v>
+        <v>-4.2173</v>
       </c>
       <c r="M28" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8750999999999999</v>
+        <v>0.8751000000000001</v>
       </c>
       <c r="O28" t="n">
         <v>7.584500000000001</v>
@@ -2638,13 +2638,13 @@
         <v>14.8667</v>
       </c>
       <c r="S28" t="n">
-        <v>7.230799999999998</v>
+        <v>7.909799999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>5.2502</v>
+        <v>5.2505</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9804</v>
+        <v>2.6596</v>
       </c>
       <c r="V28" t="n">
         <v>15.1592</v>
